--- a/data/Mörel-Filet/investment_decision/Mörel_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Mörel_SFH_2005-2014_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>21.73147444212627</v>
+        <v>13.19225960813973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>3336.892480505539</v>
       </c>
       <c r="F2" t="n">
-        <v>21.51265470448438</v>
+        <v>13.19225960813973</v>
       </c>
       <c r="G2" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="H2" t="n">
-        <v>18.86658814133234</v>
+        <v>13.19225960813973</v>
       </c>
       <c r="I2" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="J2" t="n">
-        <v>21.56699279769927</v>
+        <v>13.19225960813973</v>
       </c>
       <c r="K2" t="n">
         <v>3336.892480505539</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>21.73147444212627</v>
+        <v>15.37073142791077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>3336.892480505539</v>
       </c>
       <c r="F3" t="n">
-        <v>21.51265470448438</v>
+        <v>14.11896380481112</v>
       </c>
       <c r="G3" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="H3" t="n">
-        <v>20.53634474351462</v>
+        <v>14.13146406611979</v>
       </c>
       <c r="I3" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="J3" t="n">
-        <v>21.56699279769926</v>
+        <v>15.37484231126793</v>
       </c>
       <c r="K3" t="n">
         <v>3336.892480505539</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>21.73147444212627</v>
+        <v>15.37073142791077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>3336.892480505539</v>
       </c>
       <c r="F4" t="n">
-        <v>21.51265470448438</v>
+        <v>14.11896380481112</v>
       </c>
       <c r="G4" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="H4" t="n">
-        <v>20.53634474351462</v>
+        <v>14.13146406611979</v>
       </c>
       <c r="I4" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="J4" t="n">
-        <v>21.56699279769927</v>
+        <v>15.37484231126793</v>
       </c>
       <c r="K4" t="n">
         <v>3336.892480505539</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>21.73147444212627</v>
+        <v>15.37073142791077</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>3336.892480505539</v>
       </c>
       <c r="F5" t="n">
-        <v>21.51265470448438</v>
+        <v>14.11896380481112</v>
       </c>
       <c r="G5" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="H5" t="n">
-        <v>20.53634474351462</v>
+        <v>14.13146406611979</v>
       </c>
       <c r="I5" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="J5" t="n">
-        <v>21.56699279769927</v>
+        <v>15.37484231126793</v>
       </c>
       <c r="K5" t="n">
         <v>3336.892480505539</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>21.73147444212627</v>
+        <v>15.37073142791077</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>3336.892480505539</v>
       </c>
       <c r="F6" t="n">
-        <v>21.51265470448438</v>
+        <v>14.11896380481112</v>
       </c>
       <c r="G6" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="H6" t="n">
-        <v>20.53634474351462</v>
+        <v>14.13146406611979</v>
       </c>
       <c r="I6" t="n">
         <v>3336.892480505539</v>
       </c>
       <c r="J6" t="n">
-        <v>21.56699279769927</v>
+        <v>15.37484231126793</v>
       </c>
       <c r="K6" t="n">
         <v>3336.892480505539</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.87423592544436</v>
+        <v>3.882222722652208</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.87423592544436</v>
+        <v>3.882222722652208</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.716939617515221</v>
+        <v>5.020460329683237</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.716939617515221</v>
+        <v>5.020460329683237</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.09223168287807</v>
+        <v>5.527366311507775</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.09223168287807</v>
+        <v>5.527366311507775</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.297881941890628</v>
+        <v>5.80513756243055</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.297881941890628</v>
+        <v>5.80513756243055</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.005338720758308</v>
+        <v>6.760697528089888</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.42556671150965</v>
+        <v>5.977601036831993</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.42556671150965</v>
+        <v>5.977601036831993</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00104665824</v>
+        <v>0.00100115136</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00109216512</v>
+        <v>0.00100115136</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2417553</v>
+        <v>0.2581927920776083</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2417553</v>
+        <v>0.2581927920776083</v>
       </c>
       <c r="G18" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2417553</v>
+        <v>0.2340172620776083</v>
       </c>
       <c r="I18" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2417553</v>
+        <v>0.2340172620776082</v>
       </c>
       <c r="K18" t="n">
         <v>0.812297808</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2417553</v>
+        <v>0.2581927920776083</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2417553</v>
+        <v>0.2581927920776083</v>
       </c>
       <c r="G19" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2417553</v>
+        <v>0.2340172620776083</v>
       </c>
       <c r="I19" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2417553</v>
+        <v>0.2340172620776082</v>
       </c>
       <c r="K19" t="n">
         <v>0.812297808</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.315102216812981</v>
+        <v>0.2659037932872814</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F20" t="n">
-        <v>0.315102216812981</v>
+        <v>0.2581927920776083</v>
       </c>
       <c r="G20" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H20" t="n">
-        <v>0.315102216812981</v>
+        <v>0.2340172620776083</v>
       </c>
       <c r="I20" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J20" t="n">
-        <v>0.315102216812981</v>
+        <v>0.2340172620776082</v>
       </c>
       <c r="K20" t="n">
         <v>0.812297808</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07334691681298094</v>
+        <v>0.122056591328804</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07334691681298097</v>
+        <v>0.1255942010761997</v>
       </c>
       <c r="G21" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07334691681298097</v>
+        <v>0.1271599831348</v>
       </c>
       <c r="I21" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07334691681298094</v>
+        <v>0.114296341140429</v>
       </c>
       <c r="K21" t="n">
         <v>0.812297808</v>
@@ -1477,13 +1477,13 @@
         <v>0.812297808</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.02417553000000003</v>
       </c>
       <c r="I28" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.02417553000000003</v>
       </c>
       <c r="K28" t="n">
         <v>0.812297808</v>
@@ -1508,19 +1508,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.007738037922391653</v>
       </c>
       <c r="G29" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.03211974198457454</v>
       </c>
       <c r="I29" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.02417553000000003</v>
       </c>
       <c r="K29" t="n">
         <v>0.812297808</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.05489993704180057</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.06261093825147362</v>
       </c>
       <c r="G30" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.08678646825147371</v>
       </c>
       <c r="I30" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.08678646825147374</v>
       </c>
       <c r="K30" t="n">
         <v>0.812297808</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.05489993704180057</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.812297808</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.06635868492691922</v>
       </c>
       <c r="G31" t="n">
         <v>0.812297808</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.06624425686519998</v>
       </c>
       <c r="I31" t="n">
         <v>0.812297808</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.06261093825147371</v>
       </c>
       <c r="K31" t="n">
         <v>0.812297808</v>
@@ -2365,13 +2365,13 @@
         <v>5.836889401437302</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4646573746252977</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>1.57263630521774</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6190102026885977</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>1.57263630521774</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.8387444723505416</v>
+        <v>1.088095677057183</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8656447653819939</v>
+        <v>1.053832637484541</v>
       </c>
       <c r="G53" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H53" t="n">
-        <v>1.417945541240044</v>
+        <v>1.054174791203797</v>
       </c>
       <c r="I53" t="n">
         <v>2.320061520491827</v>
       </c>
       <c r="J53" t="n">
-        <v>1.530733080954251</v>
+        <v>1.088208199027352</v>
       </c>
       <c r="K53" t="n">
         <v>2.320061520491827</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.8387444723505416</v>
+        <v>1.128285971330383</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8656447653819939</v>
+        <v>1.053832637484541</v>
       </c>
       <c r="G54" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H54" t="n">
-        <v>1.417945541240044</v>
+        <v>1.054174791203797</v>
       </c>
       <c r="I54" t="n">
         <v>2.748592765584324</v>
       </c>
       <c r="J54" t="n">
-        <v>1.530733080954251</v>
+        <v>1.128250020904441</v>
       </c>
       <c r="K54" t="n">
         <v>2.748592765584324</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.720833069961511</v>
+        <v>1.743642434385514</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F55" t="n">
-        <v>1.654699788205215</v>
+        <v>1.625503409312745</v>
       </c>
       <c r="G55" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H55" t="n">
-        <v>1.597255844630736</v>
+        <v>1.626065567358407</v>
       </c>
       <c r="I55" t="n">
         <v>3.02431237372074</v>
       </c>
       <c r="J55" t="n">
-        <v>1.719949124303025</v>
+        <v>1.738772860855884</v>
       </c>
       <c r="K55" t="n">
         <v>3.02431237372074</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.679351650146911</v>
+        <v>1.630142312857173</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F56" t="n">
-        <v>1.60863713712187</v>
+        <v>1.611719128762445</v>
       </c>
       <c r="G56" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H56" t="n">
-        <v>1.610777695781236</v>
+        <v>1.611765453260235</v>
       </c>
       <c r="I56" t="n">
         <v>3.215975814583113</v>
       </c>
       <c r="J56" t="n">
-        <v>1.6785578027699</v>
+        <v>1.630157547307262</v>
       </c>
       <c r="K56" t="n">
         <v>3.215975814583113</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2372719268876954</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3147331247700194</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5452385554973151</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3313179776612149</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>5.836889401437302</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.6867116738740684</v>
+        <v>0.1875412966064035</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7372725787249406</v>
+        <v>0.2567350071161323</v>
       </c>
       <c r="G63" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7760025258288588</v>
+        <v>0.2560440326522397</v>
       </c>
       <c r="I63" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7077793187324769</v>
+        <v>0.1873140601228057</v>
       </c>
       <c r="K63" t="n">
         <v>5.836889401437302</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.6867116738740684</v>
+        <v>0.2749163410856015</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7372725787249406</v>
+        <v>0.3603166114705642</v>
       </c>
       <c r="G64" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7760025258288588</v>
+        <v>0.3598651406825938</v>
       </c>
       <c r="I64" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7077793187324769</v>
+        <v>0.2749163410856015</v>
       </c>
       <c r="K64" t="n">
         <v>5.836889401437302</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.7526793432695897</v>
+        <v>0.3593217670909961</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8236395310032814</v>
+        <v>0.488407728702885</v>
       </c>
       <c r="G65" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H65" t="n">
-        <v>0.835320507550783</v>
+        <v>0.4877362535885094</v>
       </c>
       <c r="I65" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7571915604963186</v>
+        <v>0.3641553901946841</v>
       </c>
       <c r="K65" t="n">
         <v>5.836889401437302</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.138691933415732</v>
+        <v>0.7108640241902684</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F66" t="n">
-        <v>1.214233352418168</v>
+        <v>0.7412159476248207</v>
       </c>
       <c r="G66" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H66" t="n">
-        <v>1.233629042897841</v>
+        <v>0.7404418817315834</v>
       </c>
       <c r="I66" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="J66" t="n">
-        <v>1.143114052360986</v>
+        <v>0.710670072168434</v>
       </c>
       <c r="K66" t="n">
         <v>5.836889401437302</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1771803958007092</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1771803958007092</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3000761744245228</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3000761744245228</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.395044350275378</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.395044350275378</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4722536216195556</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.4722536216195556</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5370604246155141</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5370604246155141</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.948056267006491</v>
+        <v>0.6997618890605254</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8754219751015616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="G77" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H77" t="n">
-        <v>0.238628285112616</v>
+        <v>0.6997618890605255</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1771803958007092</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J77" t="n">
-        <v>0.238628285112616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1771803958007092</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.948056267006491</v>
+        <v>0.6997618890605254</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8754219751015616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="G78" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3059275012786322</v>
+        <v>0.6997618890605255</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3000761744245228</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J78" t="n">
-        <v>0.238628285112616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="K78" t="n">
-        <v>0.3000761744245228</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.948056267006491</v>
+        <v>0.6997618890605254</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>5.836889401437302</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8754219751015616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="G79" t="n">
         <v>5.836889401437302</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3059275012786322</v>
+        <v>0.6997618890605255</v>
       </c>
       <c r="I79" t="n">
-        <v>0.395044350275378</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J79" t="n">
-        <v>0.238628285112616</v>
+        <v>0.6997618890605253</v>
       </c>
       <c r="K79" t="n">
-        <v>0.395044350275378</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="80">
@@ -3401,16 +3401,16 @@
         <v>5.836889401437302</v>
       </c>
       <c r="H80" t="n">
-        <v>0.06729921616601614</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4722536216195556</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.4722536216195556</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5370604246155141</v>
+        <v>5.836889401437302</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5370604246155141</v>
+        <v>5.836889401437302</v>
       </c>
     </row>
     <row r="82">
